--- a/reports/2026-10-24_report.xlsx
+++ b/reports/2026-10-24_report.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -568,22 +568,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>roma</t>
+          <t>tottenham hotspur</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -593,33 +593,37 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Winamax (FR)</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.4194767026863396</v>
+        <v>0.6227764948309646</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.04191098948573712</v>
+        <v>0.01801691343998363</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.3775657132006025</v>
+        <v>0.604759581390981</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>14.10116129670823</v>
+        <v>33.25270721570305</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Betclic (FR)': draw @ 75.00 vs market median 6.79 - price looks wrong; dropped bookmaker 'Nordic Bet': draw @ 23.00 vs market median 6.79 - price looks wrong; dropped bookmaker 'Betsson': draw @ 26.00 vs market median 6.79 - price looks wrong; already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -637,17 +641,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>borussia dortmund</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ein frankfurt</t>
+          <t>tottenham hotspur</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -666,24 +670,28 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.45</v>
+        <v>7.5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.6957732736315393</v>
+        <v>0.6471780813521226</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.379746835443038</v>
+        <v>0.1636994544737421</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.3160264381885013</v>
+        <v>0.4834786268783805</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.7046445203972713</v>
+        <v>3.853835610140919</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Betclic (FR)': draw @ 75.00 vs market median 6.79 - price looks wrong; dropped bookmaker 'Nordic Bet': draw @ 23.00 vs market median 6.79 - price looks wrong; dropped bookmaker 'Betsson': draw @ 26.00 vs market median 6.79 - price looks wrong</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -696,22 +704,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>willem ii</t>
+          <t>alverca</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>cambuur</t>
+          <t>arouca</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -726,28 +734,32 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.2552338639999342</v>
+        <v>0.4030115617996037</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.02848325273003623</v>
+        <v>0.04481720347301787</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.226750611269898</v>
+        <v>0.3581943583265859</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>13.03786251999638</v>
+        <v>11.09034685398811</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -765,17 +777,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>tottenham hotspur</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -785,33 +797,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Marathon Bet</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.6227764948309646</v>
+        <v>0.435896660947766</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.3993545070005307</v>
+        <v>0.1033439890865669</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.2234219878304339</v>
+        <v>0.3325526718611991</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.5569412370774116</v>
+        <v>3.794863270425425</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Pinnacle': draw @ 3.12 vs market median 1.26 - price looks wrong; already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -824,58 +840,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>alverca</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>arouca</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>LeoVegas (SE)</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4030115617996037</v>
+        <v>0.4837319793472701</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1817250334575997</v>
+        <v>0.2398077487117692</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2212865283420041</v>
+        <v>0.243924230635501</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.821080932597226</v>
+        <v>1.515406292605805</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Pinnacle': draw @ 3.12 vs market median 1.26 - price looks wrong</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -888,22 +908,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>willem ii</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>cambuur</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -913,33 +933,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.35</v>
+        <v>26</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.435896660947766</v>
+        <v>0.2552338639999342</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2464678625816967</v>
+        <v>0.03571428571428572</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1894287983660693</v>
+        <v>0.2195195782856485</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8961504751227818</v>
+        <v>5.636080463998289</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Betclic (FR)': draw @ 75.00 vs market median 26.00 - price looks wrong; dropped bookmaker 'Betclic (FR)': home @ 100.00 vs market median 26.00 - price looks wrong; already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -952,22 +976,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>borussia dortmund</t>
+          <t>willem ii</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ein frankfurt</t>
+          <t>cambuur</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -977,33 +1001,37 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.73</v>
+        <v>26</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.7516488695068414</v>
+        <v>0.2201896004811725</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.5665202207787814</v>
+        <v>0.03571428571428572</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.18512864872806</v>
+        <v>0.1844753147668867</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3003525442468356</v>
+        <v>4.724929612510484</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Betclic (FR)': draw @ 75.00 vs market median 26.00 - price looks wrong; dropped bookmaker 'Betclic (FR)': home @ 100.00 vs market median 26.00 - price looks wrong; already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1056,10 +1084,10 @@
         <v>0.6652122816644435</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.4931982919564672</v>
+        <v>0.489972414450355</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1720139897079762</v>
+        <v>0.1752398672140885</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0.3304245633288869</v>
@@ -1067,7 +1095,11 @@
       <c r="O9" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1080,22 +1112,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>roma</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1105,33 +1137,37 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2827639240840678</v>
+        <v>0.3011057294160842</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1194623814299252</v>
+        <v>0.1509466892773124</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1633015426541425</v>
+        <v>0.1501590401387718</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.827639240840678</v>
+        <v>2.312163023576926</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Pinnacle': draw @ 3.12 vs market median 1.26 - price looks wrong</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1144,58 +1180,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>willem ii</t>
+          <t>gil vicente</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>cambuur</t>
+          <t>porto</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>21</v>
+        <v>1.98</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2201896004811725</v>
+        <v>0.641924016296795</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06495371356390069</v>
+        <v>0.4942635803996084</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1552358869172718</v>
+        <v>0.1476604358971865</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.623981610104622</v>
+        <v>0.2710095522676541</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1208,58 +1248,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>gil vicente</t>
+          <t>borussia dortmund</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>porto</t>
+          <t>ein frankfurt</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>2.04</v>
+        <v>180</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.641924016296795</v>
+        <v>0.1159108584677515</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4949070154505749</v>
+        <v>0.007958128845716809</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1470170008462201</v>
+        <v>0.1079527296220346</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3095249932454618</v>
+        <v>19.86395452419526</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>dropped bookmaker 'Winamax (FR)': away @ 600.00 vs market median 165.00 - price looks wrong; dropped bookmaker 'Tipico': away @ 400.00 vs market median 165.00 - price looks wrong; dropped bookmaker 'Winamax (DE)': away @ 1000.00 vs market median 165.00 - price looks wrong</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1272,58 +1316,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>alverca</t>
+          <t>ath madrid</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>arouca</t>
+          <t>deportivo la coruna</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.54</v>
+        <v>1.35</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5376364891069109</v>
+        <v>0.8396192914196694</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4165420923389406</v>
+        <v>0.7433538886898516</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1210943967679703</v>
+        <v>0.09626540272981776</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3655966823315535</v>
+        <v>0.1334860434165537</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>limited history for a promoted/new team: league-average strength assumed; already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1370,24 +1418,28 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.4455241313283658</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3455160986389406</v>
+        <v>0.3537620700973331</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1000080326894252</v>
+        <v>0.09176206123103264</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2296466024662893</v>
+        <v>0.185094189333453</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>already picked in an earlier run today</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1400,22 +1452,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ath madrid</t>
+          <t>alverca</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>deportivo la coruna</t>
+          <t>arouca</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1425,169 +1477,33 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.34</v>
+        <v>6</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8396192914196694</v>
+        <v>0.2377509318360857</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7475400601789075</v>
+        <v>0.1754459304237747</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.09207923124076189</v>
+        <v>0.06230500141231099</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.125089850502357</v>
+        <v>0.4265055910165141</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>limited history for a promoted/new team: league-average strength assumed</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Tipico</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0.5162680206527299</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.4549554736460237</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.06131254700670619</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0.1357896454360059</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>ath madrid</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>deportivo la coruna</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0.671846898296485</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.6198891715249631</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>0.05195772677152188</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0.1085473821892002</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>limited history for a promoted/new team: league-average strength assumed</t>
-        </is>
-      </c>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
@@ -1601,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1752,18 +1668,18 @@
         <v>0.6227764948309646</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.3993545070005307</v>
+        <v>0.01801691343998363</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>2.5</v>
+        <v>55</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Winamax (FR)</t>
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.2234219878304339</v>
+        <v>0.604759581390981</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1687,10 @@
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.08258938442032468</v>
+        <v>0.07491944586833918</v>
       </c>
     </row>
     <row r="3">
@@ -1819,25 +1735,25 @@
         <v>0.1923015596994957</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.3368492807743524</v>
+        <v>0.1494868828655704</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Winamax (DE)</t>
         </is>
       </c>
       <c r="N3" s="6" t="n">
-        <v>-0.1445477210748567</v>
+        <v>0.04281467683392529</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.08258938442032468</v>
+        <v>0.07491944586833918</v>
       </c>
     </row>
     <row r="4">
@@ -1882,31 +1798,31 @@
         <v>0.1849219454695397</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.2637962122251169</v>
+        <v>0.8324962036944459</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.95</v>
+        <v>1.14</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-0.07887426675557715</v>
+        <v>-0.6475742582249061</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0.08258938442032468</v>
+        <v>0.07491944586833918</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1916,47 +1832,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ath madrid v deportivo la coruna</t>
+          <t>chelsea v tottenham hotspur</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.53</v>
+        <v>1.13</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.8396192914196694</v>
+        <v>0.6471780813521226</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.7475400601789075</v>
+        <v>0.1636994544737421</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.34</v>
+        <v>7.5</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.09207923124076189</v>
+        <v>0.4834786268783805</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -1964,16 +1880,16 @@
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.05434601328308186</v>
+        <v>0.0944663091379894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1983,184 +1899,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ath madrid v deportivo la coruna</t>
+          <t>chelsea v tottenham hotspur</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.53</v>
+        <v>1.13</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.09982632334094135</v>
+        <v>0.3528219186478774</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.1598893314465054</v>
+        <v>0.8363005455262579</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>6.5</v>
+        <v>1.15</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Marathon Bet</t>
         </is>
       </c>
       <c r="N6" s="6" t="n">
-        <v>-0.060063008105564</v>
+        <v>-0.4834786268783805</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>0.0944663091379894</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ath madrid v deportivo la coruna</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Home (1)</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.8396192914196694</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.7433538886898516</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1xBet</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0.09626540272981776</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v>0.05434601328308186</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="Q7" s="4" t="n">
+        <v>0.05682869267699499</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>ath madrid v deportivo la coruna</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D8" s="5" t="n">
         <v>2.93</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.53</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>15</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Away (2)</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0.06055438523938921</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>0.09257060837458725</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Unibet (SE)</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>-0.03201622313519804</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Draw (X)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.09982632334094135</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0.161189244565543</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Winamax (DE)</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>-0.0613629212246016</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>18</v>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v>0.05434601328308186</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ath madrid v deportivo la coruna</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0.671846898296485</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0.6198891715249631</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0.05195772677152188</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0.04544649127142425</v>
+      <c r="Q8" s="6" t="n">
+        <v>0.05682869267699499</v>
       </c>
     </row>
     <row r="9">
@@ -2193,37 +2109,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.328153101703515</v>
+        <v>0.06055438523938921</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.3801108284750369</v>
+        <v>0.09545686674460543</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2.61</v>
+        <v>12</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Betsson</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>-0.05195772677152188</v>
+        <v>-0.03490248150521622</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.04544649127142425</v>
+        <v>0.05682869267699499</v>
       </c>
     </row>
     <row r="10">
@@ -2239,54 +2155,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>valencia v villarreal</t>
+          <t>ath madrid v deportivo la coruna</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.15</v>
+        <v>2.93</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.46</v>
+        <v>0.53</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.3011057294160842</v>
+        <v>0.671846898296485</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.4653627164329424</v>
+        <v>0.6235485354486793</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4.02</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-0.1642569870168581</v>
+        <v>0.04829836284780575</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0.08044778913358919</v>
+        <v>0.07330125467582925</v>
       </c>
     </row>
     <row r="11">
@@ -2302,54 +2218,54 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>valencia v villarreal</t>
+          <t>ath madrid v deportivo la coruna</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1.15</v>
+        <v>2.93</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.46</v>
+        <v>0.53</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.2629976096361499</v>
+        <v>0.328153101703515</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.2881694209853609</v>
+        <v>0.3764514645513208</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Betsson</t>
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>-0.02517181134921098</v>
+        <v>-0.04829836284780581</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0.08044778913358919</v>
+        <v>0.07330125467582925</v>
       </c>
     </row>
     <row r="12">
@@ -2387,25 +2303,25 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.435896660947766</v>
+        <v>0.3011057294160842</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2464678625816967</v>
+        <v>0.1509466892773124</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4.35</v>
+        <v>11</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1894287983660693</v>
+        <v>0.1501590401387718</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2413,10 +2329,10 @@
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.08044778913358919</v>
+        <v>0.0906663522554034</v>
       </c>
     </row>
     <row r="13">
@@ -2449,37 +2365,37 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.4837319793472701</v>
+        <v>0.2629976096361499</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.5450445263539763</v>
+        <v>0.7457093216361207</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Betclic (FR)</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-0.06131254700670613</v>
+        <v>-0.4827117119999708</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.08043604567256453</v>
+        <v>0.0906663522554034</v>
       </c>
     </row>
     <row r="14">
@@ -2512,110 +2428,114 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.435896660947766</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.1033439890865669</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Marathon Bet</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.3325526718611991</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.0906663522554034</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>valencia v villarreal</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>Over/Under 2.5 goals</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0.5162680206527299</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0.4549554736460237</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Tipico</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.06131254700670619</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.4837319793472701</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.2398077487117692</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>LeoVegas (SE)</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.243924230635501</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0.08043604567256453</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>lazio v parma</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F15" t="n">
-        <v>13</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.6373162876190375</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0.6565782542044449</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>-0.01926196658540746</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0.05622789579630212</v>
+      <c r="P15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0.08832319501892316</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2625,54 +2545,54 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lazio v parma</t>
+          <t>valencia v villarreal</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.55</v>
+        <v>1.46</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.2170793269650319</v>
+        <v>0.5162680206527299</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.2154790090091032</v>
+        <v>0.7601922512882308</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.7</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.00160031795592866</v>
+        <v>-0.2439242306355008</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0.05622789579630212</v>
+        <v>0.08832319501892316</v>
       </c>
     </row>
     <row r="17">
@@ -2710,32 +2630,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.1456043854159307</v>
+        <v>0.6373162876190375</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1279427367864518</v>
+        <v>0.6561233672536729</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>8.6</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>BetOnline.ag</t>
         </is>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.01766164862947897</v>
+        <v>-0.01880707963463546</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.05622789579630212</v>
+        <v>0.06263785479936486</v>
       </c>
     </row>
     <row r="18">
@@ -2768,104 +2688,100 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.3347877183355566</v>
+        <v>0.2170793269650319</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.5068017080435328</v>
+        <v>0.2156495510016676</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>1.99</v>
+        <v>4.75</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N18" s="6" t="n">
-        <v>-0.1720139897079762</v>
+        <v>0.001429775963364299</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0.05415253206066579</v>
+        <v>0.06263785479936486</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>lazio v parma</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>1.49</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" t="n">
         <v>13</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0.6652122816644435</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0.4931982919564672</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>0.1720139897079762</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>0.05415253206066579</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.1456043854159307</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0.1282270817446595</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>0.01737730367127127</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0.06263785479936486</v>
       </c>
     </row>
     <row r="20">
@@ -2881,54 +2797,54 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>napoli v roma</t>
+          <t>lazio v parma</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.88</v>
+        <v>1.49</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.21</v>
+        <v>0.55</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2977593732295925</v>
+        <v>0.3347877183355566</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.8386266290843376</v>
+        <v>0.510027585549645</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1.16</v>
+        <v>1.94</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N20" s="6" t="n">
-        <v>-0.5408672558547452</v>
+        <v>-0.1752398672140884</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0.06903224499790497</v>
+        <v>0.05712116978446831</v>
       </c>
     </row>
     <row r="21">
@@ -2944,261 +2860,257 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>napoli v roma</t>
+          <t>lazio v parma</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.88</v>
+        <v>1.49</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.21</v>
+        <v>0.55</v>
       </c>
       <c r="F21" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Over/Under 2.5 goals</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Under 2.5</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.6652122816644435</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.489972414450355</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1xBet</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0.1752398672140885</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0.05712116978446831</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>borussia dortmund v ein frankfurt</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Home (1)</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.7516488695068414</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0.909182418198892</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>-0.1575335486920506</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>-0.0758451693326042</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>borussia dortmund v ein frankfurt</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="n">
         <v>11</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Draw (X)</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0.2827639240840678</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.1194623814299252</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Matchbook</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0.1633015426541425</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="J23" s="6" t="n">
+        <v>0.1324402720254071</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0.08285945295539113</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Coolbet</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0.04958081907001596</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>-0.0758451693326042</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>borussia dortmund v ein frankfurt</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0.1159108584677515</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.007958128845716809</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Bet</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.1079527296220346</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="P21" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0.06903224499790497</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>napoli v roma</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F22" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Away (2)</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>0.4194767026863396</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0.04191098948573712</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Matchbook</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0.3775657132006025</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>0.06903224499790497</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Germany Bundesliga</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>borussia dortmund v ein frankfurt</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>0.7516488695068414</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0.5665202207787814</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Matchbook</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>0.18512864872806</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>0.08577247574227385</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Germany Bundesliga</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>borussia dortmund v ein frankfurt</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F24" t="n">
-        <v>11</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Draw (X)</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.1324402720254071</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.2751866519276449</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>888sport</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>-0.1427463799022378</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>0.08577247574227385</v>
+      <c r="Q24" s="4" t="n">
+        <v>-0.0758451693326042</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3208,20 +3120,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>borussia dortmund v ein frankfurt</t>
+          <t>lens v paris saint germain</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2.69</v>
+        <v>1.54</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3230,105 +3142,101 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.1159108584677515</v>
+        <v>0.3881874894877736</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.1582931272935738</v>
+        <v>0.4039197921739499</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>7</v>
+        <v>2.52</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>GTbets</t>
         </is>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-0.04238226882582236</v>
+        <v>-0.01573230268617626</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.08577247574227385</v>
+        <v>0.06078329161286062</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Germany Bundesliga</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>borussia dortmund v ein frankfurt</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G26" s="2" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lens v paris saint germain</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F26" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0.6957732736315393</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0.379746835443038</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="G26" t="n">
+        <v>12</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Draw (X)</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.2444149395467488</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0.2695394409488845</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Unibet (SE)</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
-        <v>0.3160264381885013</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0.07482993197278898</v>
+      <c r="N26" s="6" t="n">
+        <v>-0.02512450140213571</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>0.06078329161286062</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3338,54 +3246,54 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>borussia dortmund v ein frankfurt</t>
+          <t>lens v paris saint germain</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2.69</v>
+        <v>1.54</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.3042267263684607</v>
+        <v>0.3673975709654778</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.6202531645569621</v>
+        <v>0.3265407668771657</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.3160264381885014</v>
+        <v>0.0408568040883121</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.07482993197278898</v>
+        <v>0.06078329161286062</v>
       </c>
     </row>
     <row r="28">
@@ -3418,37 +3326,37 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.3881874894877736</v>
+        <v>0.5819209941221337</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.3774085249706805</v>
+        <v>0.5791137231555087</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.01077896451709309</v>
+        <v>0.002807270966625031</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0.05744240165668233</v>
+        <v>0.06453482285863033</v>
       </c>
     </row>
     <row r="29">
@@ -3481,43 +3389,43 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.2444149395467488</v>
+        <v>0.4180790058778663</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.2670902671740845</v>
+        <v>0.4208862768444913</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N29" s="6" t="n">
-        <v>-0.02267532762733568</v>
+        <v>-0.002807270966624975</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.05744240165668233</v>
+        <v>0.06453482285863033</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3527,21 +3435,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lens v paris saint germain</t>
+          <t>den haag v heerenveen</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
         <v>7</v>
       </c>
-      <c r="G30" t="n">
-        <v>12</v>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
@@ -3549,38 +3457,38 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.3673975709654778</v>
+        <v>0.2749474319679151</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.3555012078552351</v>
+        <v>0.2814399535884158</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Unibet (NL)</t>
         </is>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.01189636311024267</v>
+        <v>-0.006492521620500735</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.05744240165668233</v>
+        <v>0.07810735568204523</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3590,60 +3498,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lens v paris saint germain</t>
+          <t>den haag v heerenveen</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
         <v>7</v>
       </c>
-      <c r="G31" t="n">
-        <v>12</v>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.5819209941221337</v>
+        <v>0.2643390677970682</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.578035167119154</v>
+        <v>0.2453445503296281</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>1.69</v>
+        <v>4</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.00388582700297968</v>
+        <v>0.01899451746744008</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.06314615248990792</v>
+        <v>0.07810735568204523</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3653,54 +3561,54 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lens v paris saint germain</t>
+          <t>den haag v heerenveen</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
         <v>7</v>
       </c>
-      <c r="G32" t="n">
-        <v>12</v>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.4180790058778663</v>
+        <v>0.4607135002350169</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.4219648328808459</v>
+        <v>0.473215496081956</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N32" s="6" t="n">
-        <v>-0.003885827002979625</v>
+        <v>-0.01250199584693912</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0.06314615248990792</v>
+        <v>0.07810735568204523</v>
       </c>
     </row>
     <row r="33">
@@ -3733,299 +3641,307 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.2749474319679151</v>
+        <v>0.5544758686716342</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.278402906555952</v>
+        <v>0.6462379299026669</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>3.6</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Unibet (NL)</t>
+          <t>Nordic Bet</t>
         </is>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.003455474588036911</v>
+        <v>-0.0917620612310327</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.07236904615832308</v>
+        <v>0.07213047904061616</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Netherlands Eredivisie</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>den haag v heerenveen</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="3" t="n">
         <v>1.72</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Over/Under 2.5 goals</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Under 2.5</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.4455241313283658</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.3537620700973331</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Bet</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.09176206123103264</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.07213047904061616</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>willem ii v cambuur</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Home (1)</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0.2552338639999342</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.03571428571428572</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Bet</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>0.2195195782856485</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>-0.9230769230769231</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>willem ii v cambuur</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Draw (X)</t>
         </is>
       </c>
-      <c r="J34" s="6" t="n">
-        <v>0.2643390677970682</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>0.2467056961682308</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Coolbet</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>0.01763337162883735</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>0.07236904615832308</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="J36" s="4" t="n">
+        <v>0.2201896004811725</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.03571428571428572</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Bet</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.1844753147668867</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>-0.9230769230769231</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Netherlands Eredivisie</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>den haag v heerenveen</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F35" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>willem ii v cambuur</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Away (2)</t>
         </is>
       </c>
-      <c r="J35" s="6" t="n">
-        <v>0.4607135002350169</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>0.4748913972758171</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Betfair</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>-0.01417789704080025</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>0.07236904615832308</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>den haag v heerenveen</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G36" t="n">
-        <v>7</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>0.5544758686716342</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>0.6544839013610595</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>William Hill</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>-0.1000080326894253</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>0.07108786603140856</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>den haag v heerenveen</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0.4455241313283658</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0.3455160986389406</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="J37" s="6" t="n">
+        <v>0.5245765355188934</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>Nordic Bet</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
-        <v>0.1000080326894252</v>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>0.07108786603140856</v>
+      <c r="N37" s="6" t="n">
+        <v>-0.4039948930525352</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>-0.9230769230769231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -4035,20 +3951,20 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>willem ii v cambuur</t>
+          <t>alverca v arouca</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -4061,21 +3977,21 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.2552338639999342</v>
+        <v>0.4030115617996037</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.02848325273003623</v>
+        <v>0.04481720347301787</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.226750611269898</v>
+        <v>0.3581943583265859</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -4083,16 +3999,16 @@
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.06227741935045824</v>
+        <v>0.1048414790669209</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4102,20 +4018,20 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>willem ii v cambuur</t>
+          <t>alverca v arouca</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -4128,21 +4044,21 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.2201896004811725</v>
+        <v>0.2377509318360857</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.06495371356390069</v>
+        <v>0.1754459304237747</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Matchbook</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.1552358869172718</v>
+        <v>0.06230500141231099</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -4150,16 +4066,16 @@
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>0.06227741935045824</v>
+        <v>0.1048414790669209</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4169,20 +4085,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>willem ii v cambuur</t>
+          <t>alverca v arouca</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4195,95 +4111,91 @@
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.5245765355188934</v>
+        <v>0.3592375063643105</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.9065630337060632</v>
+        <v>0.7797368661032074</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Betfair</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-0.3819864981871698</v>
+        <v>-0.4204993597388968</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>0.06227741935045824</v>
+        <v>0.1048414790669209</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>alverca v arouca</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Home (1)</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>0.4030115617996037</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0.1817250334575997</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Betfair</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>0.2212865283420041</v>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>0.1000589843394322</v>
+      <c r="J41" s="6" t="n">
+        <v>0.1685455547347286</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>0.1322075777164152</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Coolbet</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>0.0363379770183134</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0.08956211545059575</v>
       </c>
     </row>
     <row r="42">
@@ -4299,20 +4211,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>alverca v arouca</t>
+          <t>gil vicente v porto</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1.44</v>
+        <v>0.62</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4325,28 +4237,28 @@
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.2377509318360857</v>
+        <v>0.2188705840401574</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.2705309449651885</v>
+        <v>0.2135146452892566</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>3.75</v>
+        <v>4.67</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.03278001312910286</v>
+        <v>0.005355938750900874</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>0.1000589843394322</v>
+        <v>0.08956211545059575</v>
       </c>
     </row>
     <row r="43">
@@ -4362,20 +4274,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>alverca v arouca</t>
+          <t>gil vicente v porto</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1.44</v>
+        <v>0.62</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4388,477 +4300,158 @@
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.3592375063643105</v>
+        <v>0.612583861225114</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.5477440215772118</v>
+        <v>0.6542777769943282</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>3.1</v>
+        <v>1.45</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>William Hill</t>
+          <t>BetOnline.ag</t>
         </is>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.1885065152129013</v>
+        <v>-0.04169391576921422</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>0.1000589843394322</v>
+        <v>0.08956211545059575</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>alverca v arouca</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Over/Under 2.5 goals</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>0.5376364891069109</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>0.4165420923389406</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Matchbook</t>
-        </is>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0.1210943967679703</v>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="J44" s="6" t="n">
+        <v>0.358075983703205</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>0.5057364196003916</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>-0.1476604358971866</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v>0.07427848457075206</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Over/Under 2.5 goals</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Under 2.5</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>0.641924016296795</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>0.4942635803996084</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0.1476604358971865</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="P44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q44" s="4" t="n">
-        <v>0.09159060573537722</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>alverca v arouca</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F45" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" t="n">
-        <v>8</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>0.4623635108930891</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>0.5834579076610594</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>William Hill</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>-0.1210943967679703</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v>0.09159060573537722</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F46" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" t="n">
-        <v>15</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>0.1685455547347286</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>0.1305650347998513</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Betfair</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="n">
-        <v>0.03798051993487728</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v>0.08111772365535805</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F47" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" t="n">
-        <v>15</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Draw (X)</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>0.2188705840401574</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>0.2120071520380623</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Betfair</t>
-        </is>
-      </c>
-      <c r="N47" s="6" t="n">
-        <v>0.006863432002095188</v>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v>0.08111772365535805</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F48" t="n">
-        <v>7</v>
-      </c>
-      <c r="G48" t="n">
-        <v>15</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Away (2)</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>0.612583861225114</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>0.6574278131620865</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Betfair</t>
-        </is>
-      </c>
-      <c r="N48" s="6" t="n">
-        <v>-0.04484395193697255</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v>0.08111772365535805</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F49" t="n">
-        <v>7</v>
-      </c>
-      <c r="G49" t="n">
-        <v>15</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>0.358075983703205</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>0.5050929845494252</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Matchbook</t>
-        </is>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>-0.1470170008462202</v>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v>0.06888474544449685</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>0.641924016296795</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0.4949070154505749</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Matchbook</t>
-        </is>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>0.1470170008462201</v>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>0.06888474544449685</v>
+      <c r="P45" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0.07427848457075206</v>
       </c>
     </row>
   </sheetData>
@@ -4900,7 +4493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 19:16 SAST</t>
+          <t>2026-10-24 20:23 SAST</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -4937,7 +4530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -4947,7 +4540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
@@ -5040,7 +4633,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Spain La Liga: could not match away team 'Deportivo La Coruña' (the-odds-api)</t>
+          <t>England Premier League: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); England Premier League: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Spain La Liga: could not match away team 'Deportivo La Coruña' (the-odds-api); Spain La Liga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Spain La Liga: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Italy Serie A: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Italy Serie A: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Germany Bundesliga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); France Ligue 1: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Netherlands Eredivisie: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Netherlands Eredivisie: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Portugal Primeira Liga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Portugal Primeira Liga: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list)</t>
         </is>
       </c>
     </row>

--- a/reports/2026-10-24_report.xlsx
+++ b/reports/2026-10-24_report.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -568,32 +568,32 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>alverca</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>arouca</t>
+          <t>paris saint germain</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -602,26 +602,26 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>120</v>
+        <v>2.5</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.4030115617996037</v>
+        <v>0.5819273543633781</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.01413017857058164</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.3888813832290221</v>
+        <v>0.2148387467684413</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>47.36138741595245</v>
+        <v>0.4548183859084451</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>20</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>already picked in an earlier run today</t>
+          <t>unavailable: API-Football errors: {'plan': 'Free plans do not have access to this season, try from 2022 to 2024.'} (not faked); status 'live': not presented as upcoming</t>
         </is>
       </c>
     </row>
@@ -636,60 +636,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>willem ii</t>
+          <t>gil vicente</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>cambuur</t>
+          <t>porto</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Nordic Bet</t>
+          <t>GTbets</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>26</v>
+        <v>1.9</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.2552338639999342</v>
+        <v>0.6419242351568054</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.03571428571428572</v>
+        <v>0.506838576639113</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.2195195782856485</v>
+        <v>0.1350856585176924</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>5.636080463998289</v>
+        <v>0.2196560467979303</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>20</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>dropped bookmaker 'Betclic (FR)': draw @ 75.00 vs market median 26.00 - price looks wrong; dropped bookmaker 'Betclic (FR)': home @ 100.00 vs market median 26.00 - price looks wrong; already picked in an earlier run today</t>
+          <t>unavailable: API-Football errors: {'plan': 'Free plans do not have access to this season, try from 2022 to 2024.'} (not faked); already picked in an earlier run today</t>
         </is>
       </c>
     </row>
@@ -704,22 +704,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>ath madrid</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>deportivo la coruna</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -729,35 +729,35 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.6652122816644435</v>
+        <v>0.6718403754715576</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4791936583957151</v>
+        <v>0.5610933345104149</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1860186232687284</v>
+        <v>0.1107470409611427</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4169021599452645</v>
+        <v>0.142128638301648</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>20</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>already picked in an earlier run today</t>
+          <t>unavailable: API-Football errors: {'plan': 'Free plans do not have access to this season, try from 2022 to 2024.'} (not faked); limited history for a promoted/new team: weak-team prior assumed (heuristic); status 'live': not presented as upcoming; already picked in an earlier run today</t>
         </is>
       </c>
     </row>
@@ -772,22 +772,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>willem ii</t>
+          <t>ath madrid</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>cambuur</t>
+          <t>deportivo la coruna</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -797,35 +797,35 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Nordic Bet</t>
+          <t>Winamax (DE)</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>26</v>
+        <v>1.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.2201896004811725</v>
+        <v>0.8396138099347479</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.03571428571428572</v>
+        <v>0.7288960361362418</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1844753147668867</v>
+        <v>0.1107177737985061</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>4.724929612510484</v>
+        <v>0.09149795291517226</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>20</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>dropped bookmaker 'Betclic (FR)': draw @ 75.00 vs market median 26.00 - price looks wrong; dropped bookmaker 'Betclic (FR)': home @ 100.00 vs market median 26.00 - price looks wrong; already picked in an earlier run today</t>
+          <t>unavailable: API-Football errors: {'plan': 'Free plans do not have access to this season, try from 2022 to 2024.'} (not faked); limited history for a promoted/new team: weak-team prior assumed (heuristic); status 'live': not presented as upcoming; already picked in an earlier run today</t>
         </is>
       </c>
     </row>
@@ -840,60 +840,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>gil vicente</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>porto</t>
+          <t>paris saint germain</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>William Hill</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.641924016296795</v>
+        <v>0.3674013839559578</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.5037380437239167</v>
+        <v>0.2779717671462367</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1381859725728782</v>
+        <v>0.08942961680972111</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2260748711268783</v>
+        <v>0.2859048438458522</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>20</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>already picked in an earlier run today</t>
+          <t>unavailable: API-Football errors: {'plan': 'Free plans do not have access to this season, try from 2022 to 2024.'} (not faked); status 'live': not presented as upcoming</t>
         </is>
       </c>
     </row>
@@ -908,22 +908,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>alverca</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>arouca</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -942,162 +942,26 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>9.5</v>
+        <v>1.67</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2377509318360857</v>
+        <v>0.6373163559151604</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1139474702160639</v>
+        <v>0.5778485445647067</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1238034616200218</v>
+        <v>0.05946781135045376</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.258633852442814</v>
+        <v>0.06431831437831792</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>already picked in an earlier run today</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>den haag</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>heerenveen</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Bet</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0.4455241313283658</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.3537620700973331</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0.09176206123103264</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0.185094189333453</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>already picked in an earlier run today</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>ath madrid</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>deportivo la coruna</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0.8396192914196694</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0.7547121138794987</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0.08490717754017074</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0.1166936575881603</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>limited history for a promoted/new team: league-average strength assumed; already picked in an earlier run today</t>
+          <t>unavailable: API-Football errors: {'plan': 'Free plans do not have access to this season, try from 2022 to 2024.'} (not faked); status 'live': not presented as upcoming</t>
         </is>
       </c>
     </row>
@@ -1113,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1261,21 +1125,21 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.8396192914196694</v>
+        <v>0.8396138099347479</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.7547121138794987</v>
+        <v>0.7288960361362418</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Winamax (DE)</t>
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.08490717754017074</v>
+        <v>0.1107177737985061</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -1283,10 +1147,10 @@
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.05852168836567021</v>
+        <v>0.08500397243722145</v>
       </c>
     </row>
     <row r="3">
@@ -1328,28 +1192,28 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.09982632334094135</v>
+        <v>0.09983006803539726</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1536570983627194</v>
+        <v>0.1785433938617125</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>6.7</v>
+        <v>5.65</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N3" s="6" t="n">
-        <v>-0.05383077502177805</v>
+        <v>-0.07871332582631521</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.05852168836567021</v>
+        <v>0.08500397243722145</v>
       </c>
     </row>
     <row r="4">
@@ -1391,91 +1255,95 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.06055438523938921</v>
+        <v>0.06055612202985476</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.09163078775778193</v>
+        <v>0.09256057000204578</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-0.03107640251839271</v>
+        <v>-0.03200444797219101</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0.05852168836567021</v>
+        <v>0.08500397243722145</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Spain La Liga</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ath madrid v deportivo la coruna</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.53</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Over/Under 2.5 goals</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.671846898296485</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>0.6469414599914843</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Betsson</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.02490543830500069</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0.06633234103693075</v>
+      <c r="J5" s="4" t="n">
+        <v>0.6718403754715576</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.5610933345104149</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Coolbet</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.1107470409611427</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.0925728965141851</v>
       </c>
     </row>
     <row r="6">
@@ -1517,91 +1385,95 @@
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.328153101703515</v>
+        <v>0.3281596245284424</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0.3530585400085157</v>
+        <v>0.4389066654895851</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Betsson</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="N6" s="6" t="n">
-        <v>-0.02490543830500075</v>
+        <v>-0.1107470409611427</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0.06633234103693075</v>
+        <v>0.0925728965141851</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>lazio v parma</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Home (1)</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.6373162876190375</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>0.6670869738670701</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Pinnacle</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>-0.02977068624803259</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0.0645441049243438</v>
+      <c r="J7" s="4" t="n">
+        <v>0.6373163559151604</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.5778485445647067</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Coolbet</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0.05946781135045376</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0.0923290840605016</v>
       </c>
     </row>
     <row r="8">
@@ -1643,28 +1515,28 @@
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.2170793269650319</v>
+        <v>0.2170793267805853</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2101746154308697</v>
+        <v>0.2788692323776557</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4.8</v>
+        <v>3.53</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.006904711534162222</v>
+        <v>-0.06178990559707032</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0.0645441049243438</v>
+        <v>0.0923290840605016</v>
       </c>
     </row>
     <row r="9">
@@ -1706,34 +1578,34 @@
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.1456043854159307</v>
+        <v>0.1456043173042542</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1227384107020603</v>
+        <v>0.1432822230576378</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>8.6</v>
+        <v>7.83</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Marathon Bet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.02286597471387046</v>
+        <v>0.002322094246616391</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.0645441049243438</v>
+        <v>0.0923290840605016</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1743,247 +1615,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lazio v parma</t>
+          <t>lens v paris saint germain</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.55</v>
+        <v>1.48</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.3347877183355566</v>
+        <v>0.3881950540645549</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.5208063416042849</v>
+        <v>0.4024356787048139</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Unibet (FR)</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-0.1860186232687283</v>
+        <v>-0.01424062464025905</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0.06052645563913552</v>
+        <v>0.08878116816483889</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Italy Serie A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>lazio v parma</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lens v paris saint germain</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Draw (X)</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.2444035619794873</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0.3195925541489493</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Marathon Bet</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>-0.07518899216946201</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>0.08878116816483889</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>lens v paris saint germain</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.3674013839559578</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.2779717671462367</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Coolbet</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.08942961680972111</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0.08878116816483889</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>lens v paris saint germain</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Over/Under 2.5 goals</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.6652122816644435</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.4791936583957151</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1xBet</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0.1860186232687284</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.5819273543633781</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.3670886075949367</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Tipico</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.2148387467684413</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0.06052645563913552</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>France Ligue 1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>lens v paris saint germain</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.3881874894877736</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>0.4004400930841547</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Coolbet</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>-0.01225260359638114</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0.07909209693072647</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>France Ligue 1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lens v paris saint germain</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Draw (X)</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.2444149395467488</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>0.2686849037656793</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Coolbet</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>-0.02426996421893049</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0.07909209693072647</v>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0.08965517241379306</v>
       </c>
     </row>
     <row r="14">
@@ -2016,43 +1892,43 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.3673975709654778</v>
+        <v>0.4180726456366219</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.330875003150166</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3.11</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03652256781531177</v>
+        <v>-0.2148387467684414</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0.07909209693072647</v>
+        <v>0.08965517241379306</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2062,60 +1938,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lens v paris saint germain</t>
+          <t>den haag v heerenveen</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" t="n">
-        <v>12</v>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.5819209941221337</v>
+        <v>0.274947406687496</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5843484018703575</v>
+        <v>0.3003917292231609</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>1.67</v>
+        <v>3.55</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>William Hill</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N15" s="6" t="n">
-        <v>-0.002427407748223809</v>
+        <v>-0.02544432253566492</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.08883236113799442</v>
+        <v>0.1043509911785605</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2125,54 +2001,54 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lens v paris saint germain</t>
+          <t>den haag v heerenveen</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
         <v>7</v>
       </c>
-      <c r="G16" t="n">
-        <v>12</v>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>Draw (X)</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.4180790058778663</v>
+        <v>0.2643391654013655</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.4156515981296425</v>
+        <v>0.2688018085444721</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.002427407748223809</v>
+        <v>-0.004462643143106626</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0.08883236113799442</v>
+        <v>0.1043509911785605</v>
       </c>
     </row>
     <row r="17">
@@ -2210,32 +2086,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Away (2)</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.2749474319679151</v>
+        <v>0.4607134279111386</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.2863072981524893</v>
+        <v>0.430806462232367</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Unibet (NL)</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N17" s="6" t="n">
-        <v>-0.01135986618457424</v>
+        <v>0.02990696567877155</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.07802772584159451</v>
+        <v>0.1043509911785605</v>
       </c>
     </row>
     <row r="18">
@@ -2268,22 +2144,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Draw (X)</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.2643390677970682</v>
+        <v>0.5544754946604621</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.2472945632316681</v>
+        <v>0.5464022915016323</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2291,14 +2167,14 @@
         </is>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.01704450456540008</v>
+        <v>0.008073203158829756</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0.07802772584159451</v>
+        <v>0.0999820945649698</v>
       </c>
     </row>
     <row r="19">
@@ -2331,43 +2207,43 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Away (2)</t>
+          <t>Under 2.5</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.4607135002350169</v>
+        <v>0.4455245053395379</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.4663981386158426</v>
+        <v>0.4535977084983677</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-0.005684638380825668</v>
+        <v>-0.008073203158829756</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.07802772584159451</v>
+        <v>0.0999820945649698</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2377,834 +2253,310 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>den haag v heerenveen</t>
+          <t>gil vicente v porto</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1.18</v>
+        <v>0.62</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.5544758686716342</v>
+        <v>0.1685455930389549</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.6462379299026669</v>
+        <v>0.1308096988394526</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1.45</v>
+        <v>7.9</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nordic Bet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N20" s="6" t="n">
-        <v>-0.0917620612310327</v>
+        <v>0.03773589419950232</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0.07213047904061616</v>
+        <v>0.0927812843236115</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>den haag v heerenveen</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F21" t="n">
         <v>7</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Draw (X)</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.2188706410878882</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.2178443528767052</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>0.001026288211182974</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0.0927812843236115</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.6125837658731569</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0.6513459482838422</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Coolbet</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>-0.0387621824106853</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>0.0927812843236115</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Over/Under 2.5 goals</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.3580757648431946</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0.4931614233608869</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>-0.1350856585176923</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>0.07509387495605348</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>gil vicente v porto</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Over/Under 2.5 goals</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Under 2.5</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0.4455241313283658</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.3537620700973331</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Bet</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0.09176206123103264</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="J24" s="4" t="n">
+        <v>0.6419242351568054</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.506838576639113</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>GTbets</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.1350856585176924</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="P21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0.07213047904061616</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>willem ii v cambuur</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>0.2552338639999342</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0.03571428571428572</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Bet</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0.2195195782856485</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>-0.9230769230769231</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>willem ii v cambuur</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Draw (X)</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>0.2201896004811725</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0.03571428571428572</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Nordic Bet</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>0.1844753147668867</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>-0.9230769230769231</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Netherlands Eredivisie</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>willem ii v cambuur</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>9</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Away (2)</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.5245765355188934</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Nordic Bet</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>-0.4039948930525352</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>-0.9230769230769231</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>alverca v arouca</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0.4030115617996037</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>0.01413017857058164</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Tipico</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>0.3888813832290221</v>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="Q25" s="4" t="n">
-        <v>0.09230271378630438</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>alverca v arouca</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Draw (X)</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0.2377509318360857</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0.1139474702160639</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Coolbet</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0.1238034616200218</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>0.09230271378630438</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>alverca v arouca</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F27" t="n">
-        <v>10</v>
-      </c>
-      <c r="G27" t="n">
-        <v>8</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Away (2)</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.3592375063643105</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0.8719223512133544</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Winamax (FR)</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>-0.5126848448490439</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v>0.09230271378630438</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F28" t="n">
-        <v>7</v>
-      </c>
-      <c r="G28" t="n">
-        <v>15</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Home (1)</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>0.1685455547347286</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>0.133046941326706</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Coolbet</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>0.03549861340802263</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>0.09135358233110108</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>15</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Draw (X)</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0.2188705840401574</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>0.2159918592035654</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Pinnacle</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0.002878724836592045</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v>0.09135358233110108</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F30" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" t="n">
-        <v>15</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Match result (1X2)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Away (2)</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>0.612583861225114</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>0.6509611994697286</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Coolbet</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>-0.03837733824461464</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0.09135358233110108</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F31" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" t="n">
-        <v>15</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>0.358075983703205</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>0.4962619562760832</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Pinnacle</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>-0.1381859725728782</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>0.07368054972252355</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>gil vicente v porto</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Over/Under 2.5 goals</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Under 2.5</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>0.641924016296795</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>0.5037380437239167</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>William Hill</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>0.1381859725728782</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>VALUE</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>0.07368054972252355</v>
+      <c r="Q24" s="4" t="n">
+        <v>0.07509387495605348</v>
       </c>
     </row>
   </sheetData>
@@ -3246,7 +2598,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 20:46 SAST</t>
+          <t>2026-10-24 21:19 SAST</t>
         </is>
       </c>
     </row>
@@ -3273,7 +2625,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3283,7 +2635,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3293,7 +2645,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -3386,7 +2738,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Spain La Liga: could not match away team 'Deportivo La Coruña' (the-odds-api); Spain La Liga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Italy Serie A: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Italy Serie A: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); France Ligue 1: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Netherlands Eredivisie: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Netherlands Eredivisie: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Portugal Primeira Liga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Portugal Primeira Liga: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list)</t>
+          <t>England Premier League: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); England Premier League: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Spain La Liga: could not match away team 'Deportivo La Coruña' (the-odds-api); Spain La Liga: could not match home team 'Real Racing Club de Santander' (the-odds-api); Spain La Liga: could not match home team 'Deportivo La Coruña' (the-odds-api); Spain La Liga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Spain La Liga: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Italy Serie A: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Italy Serie A: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Germany Bundesliga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Germany Bundesliga: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); France Ligue 1: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Netherlands Eredivisie: could not match away team 'FC Twente Enschede' (the-odds-api); Netherlands Eredivisie: could not match away team 'FC Twente Enschede' (the-odds-api); Netherlands Eredivisie: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Netherlands Eredivisie: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Portugal Primeira Liga: could not match home team 'Sporting Lisbon' (the-odds-api); Portugal Primeira Liga: could not match away team 'Sporting Lisbon' (the-odds-api); Portugal Primeira Liga: bookmaker 'Betfair' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list); Portugal Primeira Liga: bookmaker 'Matchbook' excluded entirely (config odds_api.exclude_books - exchange/bad-feed list)</t>
         </is>
       </c>
     </row>
